--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDBF417-D75F-4A79-AE6F-3F6A3E36E38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270B44B8-FF78-45A7-B745-71DBC148E894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,11 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
-  <si>
-    <t>경기도</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -138,6 +134,14 @@
   </si>
   <si>
     <t>세종시는 2012년 10월 부터 데이터가 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전국</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -538,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFDF448-C804-4F09-87FE-7C4670F3AEAE}">
-  <dimension ref="A3:H23"/>
+  <dimension ref="A3:H39"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
@@ -548,145 +552,156 @@
   <sheetData>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="H4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>0</v>
       </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>2</v>
-      </c>
       <c r="G5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C12" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" t="s">
         <v>18</v>
       </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37">
+        <v>98</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C38">
+        <v>99</v>
+      </c>
+      <c r="D38" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C17" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C39">
+        <v>119</v>
+      </c>
+      <c r="D39" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C22">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C23">
-        <v>119</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A20" r:id="rId1" xr:uid="{B461A08F-BF12-4198-9B7F-4641C2B32624}"/>
-    <hyperlink ref="A13" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
+    <hyperlink ref="A36" r:id="rId1" xr:uid="{B461A08F-BF12-4198-9B7F-4641C2B32624}"/>
+    <hyperlink ref="A29" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
     <hyperlink ref="A5" r:id="rId3" xr:uid="{5E25795D-9E10-408A-ACC3-68A41599C6C7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270B44B8-FF78-45A7-B745-71DBC148E894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133E1820-E291-4083-8EDE-5ECF8C12C666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="54">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -142,6 +142,108 @@
   </si>
   <si>
     <t>전국</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공공기관 기상관측</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1F02001&amp;conn_path=I2</t>
+  </si>
+  <si>
+    <t>산업생산지수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시도별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통계청,「광업제조업동향조사」, 2025.04, 2025.06.18, 시도/산업별 광공업생산지수(2020=100)</t>
+  </si>
+  <si>
+    <t>2010년~2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시도별, 분기별 소매판매액지수를 통해, 시군구의 연간 GRDP를 월별로 분해한다. 같은 시도에 속하는 시군들은 같은 소매판매액지수를 적용한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1K41018&amp;conn_path=I2</t>
+  </si>
+  <si>
+    <t>통계청,「서비스업동향조사」, 2025 1/4, 2025.06.18, 시도별 소매판매액지수(2020=100)</t>
+  </si>
+  <si>
+    <t>소매판매액지수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업종별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분기별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">분기별 -&gt; 월별, 시도별-&gt;시군구별, </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C65_03E&amp;conn_path=I2</t>
+  </si>
+  <si>
+    <t>통계청(지역통계기획팀), 2021, 2025.06.18, GRDP(시/군/구)</t>
+  </si>
+  <si>
+    <t>연도별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010~2021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MGRDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효일수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://data.kma.go.kr/data/grnd/selectAwosRltmList.do?pgmNo=638&amp;tabNo=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지점이 91개 밖에 안되는데</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기온자료가 91개 지점에서 밖에 관측이 안되는데.. 시군구는 229개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시군구 GRDP가 연도별인데, 소매판매액지수로 분기별 GRDP로 만든 다음에, 가운데 2지점 (2,3,5,6,</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -175,12 +277,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -200,11 +314,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -542,167 +662,475 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFDF448-C804-4F09-87FE-7C4670F3AEAE}">
-  <dimension ref="A3:H39"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C3" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A2">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="H4" t="s">
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
+      <c r="K11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E12" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F12" t="s">
         <v>0</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G12" t="s">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H12" t="s">
         <v>3</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="K12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D13" t="s">
         <v>26</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E13" t="s">
         <v>5</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F13" t="s">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G13" t="s">
         <v>6</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
+      <c r="K13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="K16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" t="s">
         <v>25</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D18" t="s">
         <v>26</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C28" t="s">
+      <c r="G18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="K32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D35" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
+      <c r="K35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C36" t="s">
         <v>19</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D36" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C30" t="s">
+      <c r="K36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D37" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C31" t="s">
+      <c r="K37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D38" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C32" t="s">
+      <c r="K38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D39" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C33" t="s">
+      <c r="K39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D40" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
+      <c r="K40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K42" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D43" t="s">
         <v>15</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E43" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
+      <c r="K43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="C44" t="s">
         <v>11</v>
       </c>
-      <c r="C37">
+      <c r="D44">
         <v>98</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E44" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C38">
+      <c r="K44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D45">
         <v>99</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E45" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C39">
+      <c r="K45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D46">
         <v>119</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E46" t="s">
         <v>14</v>
+      </c>
+      <c r="K46" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K47" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="11:11" x14ac:dyDescent="0.45">
+      <c r="K49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="11:11" x14ac:dyDescent="0.45">
+      <c r="K50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="11:11" x14ac:dyDescent="0.45">
+      <c r="K51" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="11:11" x14ac:dyDescent="0.45">
+      <c r="K52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="11:11" x14ac:dyDescent="0.45">
+      <c r="K53" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A36" r:id="rId1" xr:uid="{B461A08F-BF12-4198-9B7F-4641C2B32624}"/>
-    <hyperlink ref="A29" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
-    <hyperlink ref="A5" r:id="rId3" xr:uid="{5E25795D-9E10-408A-ACC3-68A41599C6C7}"/>
+    <hyperlink ref="B43" r:id="rId1" xr:uid="{B461A08F-BF12-4198-9B7F-4641C2B32624}"/>
+    <hyperlink ref="B36" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
+    <hyperlink ref="B12" r:id="rId3" xr:uid="{5E25795D-9E10-408A-ACC3-68A41599C6C7}"/>
+    <hyperlink ref="B32" r:id="rId4" xr:uid="{DC8BFCAD-E346-486A-B4C1-EDCCCEB45CDD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeon\Desktop\[GRI] GitHub\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133E1820-E291-4083-8EDE-5ECF8C12C666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C68F68-44E3-47B6-A1E1-442E746D0536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="할일" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="56">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -244,6 +245,14 @@
   </si>
   <si>
     <t>시군구 GRDP가 연도별인데, 소매판매액지수로 분기별 GRDP로 만든 다음에, 가운데 2지점 (2,3,5,6,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이걸로 했네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기온데이터에 지점으로 된 list들을 행정 시군구로 맵핑하는 파일을 만들어 둘것.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -329,8 +338,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -346,7 +355,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -955,6 +964,9 @@
       <c r="C32" t="s">
         <v>27</v>
       </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
       <c r="H32" t="s">
         <v>51</v>
       </c>
@@ -1134,4 +1146,20 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8FCE03-E81E-4A4C-96F3-5183C14E43D9}">
+  <dimension ref="A3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeon\Desktop\[GRI] GitHub\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C68F68-44E3-47B6-A1E1-442E746D0536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED113B63-63BD-438A-A84F-AD87E4DA81E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
@@ -252,7 +252,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기온데이터에 지점으로 된 list들을 행정 시군구로 맵핑하는 파일을 만들어 둘것.</t>
+    <t>기온 데이터의 지점명 &gt;&gt; 시도와 시군구 겹치는게 있음 이거 어떻게 처리하지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -352,6 +352,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>6615</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>209668</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B95E7C4-85B1-86FE-9290-C30FC0F14BFD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5410200" y="292100"/>
+          <a:ext cx="5162815" cy="2292468"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1150,16 +1199,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8FCE03-E81E-4A4C-96F3-5183C14E43D9}">
-  <dimension ref="A3"/>
+  <dimension ref="A2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeon\Desktop\[GRI] GitHub\coolingImpact\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED113B63-63BD-438A-A84F-AD87E4DA81E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB8870C-F951-471E-9A24-8DB61723C320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="57">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -253,6 +253,10 @@
   </si>
   <si>
     <t>기온 데이터의 지점명 &gt;&gt; 시도와 시군구 겹치는게 있음 이거 어떻게 처리하지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기상자료개방포털 &gt; 기상관측 &gt; 공공기관 기상관측, 연도별 조회해서 다운</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -338,8 +342,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -404,7 +408,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -992,6 +996,9 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
       <c r="K29" t="s">
         <v>48</v>
       </c>

--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeon\Desktop\[GRI] GitHub\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB8870C-F951-471E-9A24-8DB61723C320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE27BBD2-C0BF-4403-8053-095B9B8BA14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -252,11 +252,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기온 데이터의 지점명 &gt;&gt; 시도와 시군구 겹치는게 있음 이거 어떻게 처리하지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>기상자료개방포털 &gt; 기상관측 &gt; 공공기관 기상관측, 연도별 조회해서 다운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 기온 데이터의 지점명 &gt;&gt; 시도와 시군구 겹치는게 있음 이거 어떻게 처리하지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt;한군데 임의로 지정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 한전 시군구별 월별 전력사용량 데이터에 결측치가 많음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt; 음수인 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt; 2013년까지는 MWh, 2014년부터는 kWh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt; 충남 연기군 2013년은 전기사용량이 0,1 …???</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;&gt; 2020년 대전광역시, 대덕구, 일반용의 11월 전력사용량은 음수일 뿐 아니라, 절대값 자체도 트렌드와 상이.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -327,7 +351,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -340,10 +364,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -363,15 +390,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
+      <xdr:colOff>298450</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>6615</xdr:colOff>
+      <xdr:colOff>178065</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>209668</xdr:rowOff>
+      <xdr:rowOff>152518</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -394,7 +421,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5410200" y="292100"/>
+          <a:off x="5581650" y="234950"/>
           <a:ext cx="5162815" cy="2292468"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -408,7 +435,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -997,7 +1024,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K29" t="s">
         <v>48</v>
@@ -1206,13 +1233,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8FCE03-E81E-4A4C-96F3-5183C14E43D9}">
-  <dimension ref="A2"/>
+  <dimension ref="A2:E13"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>55</v>
-      </c>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeon\Desktop\[GRI] GitHub\coolingImpact\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE27BBD2-C0BF-4403-8053-095B9B8BA14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020BD4E4-398C-4802-8830-F53E22250FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="할일" sheetId="2" r:id="rId2"/>
+    <sheet name="할일" sheetId="3" r:id="rId2"/>
+    <sheet name="데이터 있는 지역" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="73">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -176,111 +177,174 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>통계청,「서비스업동향조사」, 2025 1/4, 2025.06.18, 시도별 소매판매액지수(2020=100)</t>
+  </si>
+  <si>
+    <t>소매판매액지수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업종별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분기별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">분기별 -&gt; 월별, 시도별-&gt;시군구별, </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C65_03E&amp;conn_path=I2</t>
+  </si>
+  <si>
+    <t>통계청(지역통계기획팀), 2021, 2025.06.18, GRDP(시/군/구)</t>
+  </si>
+  <si>
+    <t>연도별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010~2021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MGRDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://data.kma.go.kr/data/grnd/selectAwosRltmList.do?pgmNo=638&amp;tabNo=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지점이 91개 밖에 안되는데</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기온자료가 91개 지점에서 밖에 관측이 안되는데.. 시군구는 229개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시군구 GRDP가 연도별인데, 소매판매액지수로 분기별 GRDP로 만든 다음에, 가운데 2지점 (2,3,5,6,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이걸로 했네</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기상자료개방포털 &gt; 기상관측 &gt; 공공기관 기상관측, 연도별 조회해서 다운</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1K41018&amp;conn_path=I2</t>
-  </si>
-  <si>
-    <t>통계청,「서비스업동향조사」, 2025 1/4, 2025.06.18, 시도별 소매판매액지수(2020=100)</t>
-  </si>
-  <si>
-    <t>소매판매액지수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>업종별</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>분기별</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">분기별 -&gt; 월별, 시도별-&gt;시군구별, </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1C65_03E&amp;conn_path=I2</t>
-  </si>
-  <si>
-    <t>통계청(지역통계기획팀), 2021, 2025.06.18, GRDP(시/군/구)</t>
-  </si>
-  <si>
-    <t>연도별</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2010~2021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MGRDP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MPS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유효일수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://data.kma.go.kr/data/grnd/selectAwosRltmList.do?pgmNo=638&amp;tabNo=1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지점이 91개 밖에 안되는데</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기온자료가 91개 지점에서 밖에 관측이 안되는데.. 시군구는 229개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시군구 GRDP가 연도별인데, 소매판매액지수로 분기별 GRDP로 만든 다음에, 가운데 2지점 (2,3,5,6,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이걸로 했네</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기상자료개방포털 &gt; 기상관측 &gt; 공공기관 기상관측, 연도별 조회해서 다운</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 기온 데이터의 지점명 &gt;&gt; 시도와 시군구 겹치는게 있음 이거 어떻게 처리하지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt;한군데 임의로 지정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 한전 시군구별 월별 전력사용량 데이터에 결측치가 많음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt; 음수인 것</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt; 2013년까지는 MWh, 2014년부터는 kWh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt; 충남 연기군 2013년은 전기사용량이 0,1 …???</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&gt;&gt; 2020년 대전광역시, 대덕구, 일반용의 11월 전력사용량은 음수일 뿐 아니라, 절대값 자체도 트렌드와 상이.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MGDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시계열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010~2021 (연도별)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산지수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1975~2025 (월별)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대구, 인천, 대전, 울산, 경북, 경남</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 지역의 시군구별 GRDP는 2015년부터 데이터가 있음.</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010.01~2021.12 (일부 지역은 2015.01~2021.12)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004.01~2024.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시군구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연도_월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시도 시군구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -288,7 +352,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,6 +374,23 @@
       <color theme="10"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -364,13 +445,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -389,23 +470,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>298450</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>178065</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>152518</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>54963</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>54096</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B95E7C4-85B1-86FE-9290-C30FC0F14BFD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{598CBFE1-F074-C494-9C53-5D3942A085B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -421,8 +502,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5581650" y="234950"/>
-          <a:ext cx="5162815" cy="2292468"/>
+          <a:off x="9264650" y="266700"/>
+          <a:ext cx="7078063" cy="866896"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -435,7 +516,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -751,150 +832,117 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FFDF448-C804-4F09-87FE-7C4670F3AEAE}">
-  <dimension ref="A1:O53"/>
+  <dimension ref="A7:T59"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10.4140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.6640625" style="2"/>
+    <col min="17" max="17" width="11.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A1">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A7">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A2">
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="D10" t="s">
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="N11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="N12" t="s">
+        <v>57</v>
+      </c>
+      <c r="O12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="N13" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" t="s">
+        <v>64</v>
+      </c>
+      <c r="P13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="K14" t="s">
+        <v>47</v>
+      </c>
+      <c r="O14" t="s">
+        <v>59</v>
+      </c>
+      <c r="P14" t="s">
+        <v>60</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="K15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O15" t="s">
+        <v>61</v>
+      </c>
+      <c r="P15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="D16" t="s">
         <v>2</v>
       </c>
-      <c r="K10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="K15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="K16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
       <c r="K17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B18" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
@@ -902,384 +950,461 @@
       <c r="E18" t="s">
         <v>4</v>
       </c>
+      <c r="F18" t="s">
+        <v>0</v>
+      </c>
       <c r="G18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K23" t="s">
+        <v>47</v>
+      </c>
+      <c r="O23" t="s">
+        <v>67</v>
+      </c>
+      <c r="P23" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>72</v>
+      </c>
+      <c r="R23" t="s">
+        <v>69</v>
+      </c>
+      <c r="S23" t="s">
+        <v>70</v>
+      </c>
+      <c r="T23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" t="s">
         <v>43</v>
       </c>
-      <c r="H18" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="K24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>33</v>
+      </c>
+      <c r="K26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" t="s">
+        <v>34</v>
+      </c>
+      <c r="J27" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="K32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K36" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K40" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="K42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B45" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" t="s">
-        <v>34</v>
-      </c>
-      <c r="J21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="D25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="C29" t="s">
-        <v>55</v>
-      </c>
-      <c r="K29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="K31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="C45" t="s">
         <v>27</v>
       </c>
-      <c r="E32" t="s">
-        <v>54</v>
-      </c>
-      <c r="H32" t="s">
-        <v>51</v>
-      </c>
-      <c r="K32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="K33" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="K34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="D35" t="s">
+      <c r="E45" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" t="s">
+        <v>49</v>
+      </c>
+      <c r="K45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K46" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="K47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="D48" t="s">
         <v>11</v>
       </c>
-      <c r="K35" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B36" s="1" t="s">
+      <c r="K48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C49" t="s">
         <v>19</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D49" t="s">
         <v>12</v>
       </c>
-      <c r="K36" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="D37" t="s">
+      <c r="K49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D50" t="s">
         <v>14</v>
       </c>
-      <c r="K37" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="D38" t="s">
+      <c r="K50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D51" t="s">
         <v>20</v>
       </c>
-      <c r="K38" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="D39" t="s">
+      <c r="K51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D52" t="s">
         <v>21</v>
       </c>
-      <c r="K39" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="D40" t="s">
+      <c r="K52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D53" t="s">
         <v>13</v>
       </c>
-      <c r="K40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="K41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="K42" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B43" s="1" t="s">
+      <c r="K53" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K54" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="K55" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B56" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C56" t="s">
         <v>18</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D56" t="s">
         <v>15</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E56" t="s">
         <v>16</v>
       </c>
-      <c r="K43" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C44" t="s">
+      <c r="K56" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="C57" t="s">
         <v>11</v>
       </c>
-      <c r="D44">
+      <c r="D57">
         <v>98</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E57" t="s">
         <v>12</v>
       </c>
-      <c r="K44" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="D45">
+      <c r="K57" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D58">
         <v>99</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E58" t="s">
         <v>13</v>
       </c>
-      <c r="K45" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="D46">
+      <c r="K58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="D59">
         <v>119</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E59" t="s">
         <v>14</v>
       </c>
-      <c r="K46" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="K47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="K48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="11:11" x14ac:dyDescent="0.45">
-      <c r="K49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="11:11" x14ac:dyDescent="0.45">
-      <c r="K50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.45">
-      <c r="K51" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52" spans="11:11" x14ac:dyDescent="0.45">
-      <c r="K52" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="11:11" x14ac:dyDescent="0.45">
-      <c r="K53" t="s">
-        <v>48</v>
+      <c r="K59" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B43" r:id="rId1" xr:uid="{B461A08F-BF12-4198-9B7F-4641C2B32624}"/>
-    <hyperlink ref="B36" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
-    <hyperlink ref="B12" r:id="rId3" xr:uid="{5E25795D-9E10-408A-ACC3-68A41599C6C7}"/>
-    <hyperlink ref="B32" r:id="rId4" xr:uid="{DC8BFCAD-E346-486A-B4C1-EDCCCEB45CDD}"/>
+    <hyperlink ref="B56" r:id="rId1" xr:uid="{B461A08F-BF12-4198-9B7F-4641C2B32624}"/>
+    <hyperlink ref="B49" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
+    <hyperlink ref="B18" r:id="rId3" xr:uid="{5E25795D-9E10-408A-ACC3-68A41599C6C7}"/>
+    <hyperlink ref="B45" r:id="rId4" xr:uid="{DC8BFCAD-E346-486A-B4C1-EDCCCEB45CDD}"/>
+    <hyperlink ref="B27" r:id="rId5" xr:uid="{FEA0B7EF-6060-47FC-8553-78F62D28FE9F}"/>
   </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId6"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F629FFE-B41C-4741-9CD5-214D95A2743F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8FCE03-E81E-4A4C-96F3-5183C14E43D9}">
-  <dimension ref="A2:E13"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83D66817-99CE-4F70-AC5E-6CCAB3E10D1A}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020BD4E4-398C-4802-8830-F53E22250FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7863855-995C-4B1A-A7A4-6AA5C9823CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -147,10 +147,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>공공기관 기상관측</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://kosis.kr/statHtml/statHtml.do?orgId=101&amp;tblId=DT_1F02001&amp;conn_path=I2</t>
   </si>
   <si>
@@ -223,10 +219,6 @@
   </si>
   <si>
     <t>o</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://data.kma.go.kr/data/grnd/selectAwosRltmList.do?pgmNo=638&amp;tabNo=1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -346,6 +338,16 @@
   <si>
     <t>시도 시군구</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://data.kma.go.kr/data/grnd/selectAsosRltmList.do?pgmNo=36</t>
+  </si>
+  <si>
+    <t>종관기상관측(ASOS)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.data.go.kr/data/15122362/fileData.do</t>
   </si>
 </sst>
 </file>
@@ -847,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.45">
@@ -855,67 +857,67 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="P10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="N11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P11" t="s">
         <v>64</v>
-      </c>
-      <c r="P11" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="N12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="N13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="K14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="K15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="P15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -923,18 +925,18 @@
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I17" t="s">
         <v>23</v>
       </c>
       <c r="K17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
@@ -963,10 +965,10 @@
         <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
@@ -992,59 +994,62 @@
         <v>8</v>
       </c>
       <c r="K19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
       <c r="K21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O23" t="s">
+        <v>65</v>
+      </c>
+      <c r="P23" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>70</v>
+      </c>
+      <c r="R23" t="s">
         <v>67</v>
       </c>
-      <c r="P23" t="s">
+      <c r="S23" t="s">
         <v>68</v>
       </c>
-      <c r="Q23" t="s">
-        <v>72</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="T23" t="s">
         <v>69</v>
-      </c>
-      <c r="S23" t="s">
-        <v>70</v>
-      </c>
-      <c r="T23" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
@@ -1056,122 +1061,122 @@
         <v>4</v>
       </c>
       <c r="G24" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" t="s">
         <v>42</v>
       </c>
-      <c r="H24" t="s">
-        <v>43</v>
-      </c>
       <c r="K24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
         <v>28</v>
-      </c>
-      <c r="C26" t="s">
-        <v>29</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
       </c>
       <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
         <v>30</v>
-      </c>
-      <c r="F26" t="s">
-        <v>31</v>
       </c>
       <c r="G26" t="s">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" t="s">
         <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" t="s">
         <v>37</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" t="s">
         <v>38</v>
       </c>
-      <c r="I27" t="s">
-        <v>34</v>
-      </c>
-      <c r="J27" t="s">
-        <v>39</v>
-      </c>
       <c r="K27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A30" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
@@ -1179,12 +1184,12 @@
         <v>11</v>
       </c>
       <c r="K36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
@@ -1192,70 +1197,70 @@
         <v>26</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C45" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45" t="s">
-        <v>52</v>
-      </c>
-      <c r="H45" t="s">
-        <v>49</v>
-      </c>
       <c r="K45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
@@ -1263,7 +1268,7 @@
         <v>11</v>
       </c>
       <c r="K48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.45">
@@ -1277,7 +1282,7 @@
         <v>12</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.45">
@@ -1285,7 +1290,7 @@
         <v>14</v>
       </c>
       <c r="K50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.45">
@@ -1293,7 +1298,7 @@
         <v>20</v>
       </c>
       <c r="K51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.45">
@@ -1301,7 +1306,7 @@
         <v>21</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.45">
@@ -1309,17 +1314,17 @@
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.45">
       <c r="K54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.45">
       <c r="K55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.45">
@@ -1336,7 +1341,7 @@
         <v>16</v>
       </c>
       <c r="K56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.45">
@@ -1350,7 +1355,7 @@
         <v>12</v>
       </c>
       <c r="K57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.45">
@@ -1361,7 +1366,7 @@
         <v>13</v>
       </c>
       <c r="K58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.45">
@@ -1372,7 +1377,7 @@
         <v>14</v>
       </c>
       <c r="K59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1381,11 +1386,10 @@
     <hyperlink ref="B56" r:id="rId1" xr:uid="{B461A08F-BF12-4198-9B7F-4641C2B32624}"/>
     <hyperlink ref="B49" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
     <hyperlink ref="B18" r:id="rId3" xr:uid="{5E25795D-9E10-408A-ACC3-68A41599C6C7}"/>
-    <hyperlink ref="B45" r:id="rId4" xr:uid="{DC8BFCAD-E346-486A-B4C1-EDCCCEB45CDD}"/>
-    <hyperlink ref="B27" r:id="rId5" xr:uid="{FEA0B7EF-6060-47FC-8553-78F62D28FE9F}"/>
+    <hyperlink ref="B27" r:id="rId4" xr:uid="{FEA0B7EF-6060-47FC-8553-78F62D28FE9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7863855-995C-4B1A-A7A4-6AA5C9823CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9458BB8B-2A85-49B4-8FC4-AC87D27A8F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,9 +74,6 @@
   <si>
     <t>2017~2023</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.data.go.kr/data/15065266/fileData.do</t>
   </si>
   <si>
     <t>전력판매량</t>
@@ -347,7 +344,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>https://www.data.go.kr/data/15065266/fileData.do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>https://www.data.go.kr/data/15122362/fileData.do</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계량데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -849,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.45">
@@ -857,67 +867,67 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="P10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="N11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="N12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="N13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O13" t="s">
+        <v>61</v>
+      </c>
+      <c r="P13" t="s">
         <v>62</v>
-      </c>
-      <c r="P13" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="K14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O14" t="s">
+        <v>56</v>
+      </c>
+      <c r="P14" t="s">
         <v>57</v>
       </c>
-      <c r="P14" t="s">
-        <v>58</v>
-      </c>
       <c r="S14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="K15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O15" t="s">
+        <v>58</v>
+      </c>
+      <c r="P15" t="s">
         <v>59</v>
-      </c>
-      <c r="P15" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -925,29 +935,29 @@
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
         <v>4</v>
@@ -962,24 +972,24 @@
         <v>3</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>9</v>
+      <c r="B19" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -994,368 +1004,383 @@
         <v>8</v>
       </c>
       <c r="K19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" t="s">
+        <v>75</v>
+      </c>
       <c r="K21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O23" t="s">
+        <v>64</v>
+      </c>
+      <c r="P23" t="s">
         <v>65</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
+        <v>69</v>
+      </c>
+      <c r="R23" t="s">
         <v>66</v>
       </c>
-      <c r="Q23" t="s">
-        <v>70</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="S23" t="s">
         <v>67</v>
       </c>
-      <c r="S23" t="s">
+      <c r="T23" t="s">
         <v>68</v>
-      </c>
-      <c r="T23" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
         <v>25</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
       </c>
       <c r="E24" t="s">
         <v>4</v>
       </c>
       <c r="G24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" t="s">
         <v>41</v>
       </c>
-      <c r="H24" t="s">
-        <v>42</v>
-      </c>
       <c r="K24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
         <v>27</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
         <v>28</v>
       </c>
-      <c r="D26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>29</v>
-      </c>
-      <c r="F26" t="s">
-        <v>30</v>
       </c>
       <c r="G26" t="s">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" t="s">
         <v>35</v>
       </c>
-      <c r="D27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>36</v>
       </c>
-      <c r="G27" t="s">
+      <c r="I27" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" t="s">
         <v>37</v>
       </c>
-      <c r="I27" t="s">
-        <v>33</v>
-      </c>
-      <c r="J27" t="s">
-        <v>38</v>
-      </c>
       <c r="K27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A30" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.45">
       <c r="K32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" t="s">
         <v>71</v>
       </c>
-      <c r="C45" t="s">
-        <v>72</v>
-      </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="D48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B49" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.45">
       <c r="D50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.45">
       <c r="D51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.45">
       <c r="D52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.45">
       <c r="D53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.45">
       <c r="K54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.45">
       <c r="K55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
         <v>17</v>
       </c>
-      <c r="C56" t="s">
-        <v>18</v>
-      </c>
       <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" t="s">
         <v>15</v>
       </c>
-      <c r="E56" t="s">
-        <v>16</v>
-      </c>
       <c r="K56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D57">
         <v>98</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.45">
@@ -1363,10 +1388,10 @@
         <v>99</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.45">
@@ -1374,10 +1399,10 @@
         <v>119</v>
       </c>
       <c r="E59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1387,9 +1412,11 @@
     <hyperlink ref="B49" r:id="rId2" xr:uid="{1A528629-0E66-4339-A16E-A3D9846EE103}"/>
     <hyperlink ref="B18" r:id="rId3" xr:uid="{5E25795D-9E10-408A-ACC3-68A41599C6C7}"/>
     <hyperlink ref="B27" r:id="rId4" xr:uid="{FEA0B7EF-6060-47FC-8553-78F62D28FE9F}"/>
+    <hyperlink ref="B19" r:id="rId5" xr:uid="{EB1BE903-2A1B-4E1D-B134-3D277DFDD127}"/>
+    <hyperlink ref="B21" r:id="rId6" xr:uid="{CA93708B-7298-4390-A23C-6F5C5527BA51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
 

--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9458BB8B-2A85-49B4-8FC4-AC87D27A8F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B29727-A384-459F-B93F-9433210DAFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="할일" sheetId="3" r:id="rId2"/>
-    <sheet name="데이터 있는 지역" sheetId="4" r:id="rId3"/>
+    <sheet name="계량데이터" sheetId="5" r:id="rId2"/>
+    <sheet name="할일" sheetId="3" r:id="rId3"/>
+    <sheet name="데이터 있는 지역" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="76">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -337,9 +339,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://data.kma.go.kr/data/grnd/selectAsosRltmList.do?pgmNo=36</t>
-  </si>
-  <si>
     <t>종관기상관측(ASOS)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -357,6 +356,10 @@
   </si>
   <si>
     <t>시간별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이상해보이는거</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -983,7 +986,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -1017,10 +1020,10 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
         <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>74</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -1032,7 +1035,7 @@
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K21" t="s">
         <v>45</v>
@@ -1262,11 +1265,11 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="s">
         <v>70</v>
-      </c>
-      <c r="C45" t="s">
-        <v>71</v>
       </c>
       <c r="E45" t="s">
         <v>49</v>
@@ -1414,13 +1417,30 @@
     <hyperlink ref="B27" r:id="rId4" xr:uid="{FEA0B7EF-6060-47FC-8553-78F62D28FE9F}"/>
     <hyperlink ref="B19" r:id="rId5" xr:uid="{EB1BE903-2A1B-4E1D-B134-3D277DFDD127}"/>
     <hyperlink ref="B21" r:id="rId6" xr:uid="{CA93708B-7298-4390-A23C-6F5C5527BA51}"/>
+    <hyperlink ref="B45" r:id="rId7" xr:uid="{0E10E423-2261-49D6-9769-C1FF0DCA4952}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2654018A-A738-43FC-91CA-43E842337D6E}">
+  <dimension ref="A4"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F629FFE-B41C-4741-9CD5-214D95A2743F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1430,7 +1450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83D66817-99CE-4F70-AC5E-6CCAB3E10D1A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>

--- a/data/자료확인.xlsx
+++ b/data/자료확인.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\coolingImpact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B29727-A384-459F-B93F-9433210DAFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7639EB8F-D4C6-4887-8DFC-3F453D2AE6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{108BE4F5-B61A-4A9B-822B-7C4E3084830C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="계량데이터" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId2"/>
     <sheet name="할일" sheetId="3" r:id="rId3"/>
     <sheet name="데이터 있는 지역" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="75">
   <si>
     <t>계약종별</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -356,10 +355,6 @@
   </si>
   <si>
     <t>시간별</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상해보이는거</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1425,16 +1420,10 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2654018A-A738-43FC-91CA-43E842337D6E}">
-  <dimension ref="A4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01E5CA5-F295-4639-ABC3-8313D22C0702}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
